--- a/output/pdf_financials_xlsx/MOX.xlsx
+++ b/output/pdf_financials_xlsx/MOX.xlsx
@@ -1000,7 +1000,7 @@
         <v>0.477416</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.775974</v>
       </c>
     </row>
     <row r="35">
@@ -1032,7 +1032,7 @@
         <v>0.477416</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.775974</v>
       </c>
     </row>
     <row r="37">
@@ -1224,7 +1224,7 @@
         <v>0.589174</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.161398</v>
+        <v>0.385424</v>
       </c>
     </row>
     <row r="49">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/MOX.xlsx
+++ b/output/pdf_financials_xlsx/MOX.xlsx
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.04414</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.112318</v>
       </c>
     </row>
     <row r="116">
@@ -4355,7 +4355,11 @@
           <t>Proceeds from disposal of investments</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
